--- a/Images/2/10000000StatisticalSeries.xlsx
+++ b/Images/2/10000000StatisticalSeries.xlsx
@@ -406,60 +406,60 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>576160</v>
+        <v>577294</v>
       </c>
       <c r="B2">
-        <v>1974455</v>
+        <v>1976037</v>
       </c>
       <c r="C2">
-        <v>2966256</v>
+        <v>2963861</v>
       </c>
       <c r="D2">
-        <v>2542379</v>
+        <v>2543214</v>
       </c>
       <c r="E2">
-        <v>1361068</v>
+        <v>1359233</v>
       </c>
       <c r="F2">
-        <v>466927</v>
+        <v>467309</v>
       </c>
       <c r="G2">
-        <v>99878</v>
+        <v>100298</v>
       </c>
       <c r="H2">
-        <v>12216</v>
+        <v>12087</v>
       </c>
       <c r="I2">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>0.057616</v>
+        <v>0.0577294</v>
       </c>
       <c r="B3">
-        <v>0.1974455</v>
+        <v>0.1976037</v>
       </c>
       <c r="C3">
-        <v>0.2966256</v>
+        <v>0.2963861</v>
       </c>
       <c r="D3">
-        <v>0.2542379</v>
+        <v>0.2543214</v>
       </c>
       <c r="E3">
-        <v>0.1361068</v>
+        <v>0.1359233</v>
       </c>
       <c r="F3">
-        <v>0.04669270000000003</v>
+        <v>0.04673090000000002</v>
       </c>
       <c r="G3">
-        <v>0.009987799999999991</v>
+        <v>0.01002979999999998</v>
       </c>
       <c r="H3">
-        <v>0.001221600000000045</v>
+        <v>0.001208700000000063</v>
       </c>
       <c r="I3">
-        <v>6.609999999995786E-05</v>
+        <v>6.669999999997511E-05</v>
       </c>
     </row>
   </sheetData>

--- a/Images/2/10000000StatisticalSeries.xlsx
+++ b/Images/2/10000000StatisticalSeries.xlsx
@@ -406,60 +406,60 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>577294</v>
+        <v>576109</v>
       </c>
       <c r="B2">
-        <v>1976037</v>
+        <v>1975389</v>
       </c>
       <c r="C2">
-        <v>2963861</v>
+        <v>2964294</v>
       </c>
       <c r="D2">
-        <v>2543214</v>
+        <v>2543192</v>
       </c>
       <c r="E2">
-        <v>1359233</v>
+        <v>1361027</v>
       </c>
       <c r="F2">
-        <v>467309</v>
+        <v>466671</v>
       </c>
       <c r="G2">
-        <v>100298</v>
+        <v>100345</v>
       </c>
       <c r="H2">
-        <v>12087</v>
+        <v>12323</v>
       </c>
       <c r="I2">
-        <v>667</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>0.0577294</v>
+        <v>0.0576109</v>
       </c>
       <c r="B3">
-        <v>0.1976037</v>
+        <v>0.1975389</v>
       </c>
       <c r="C3">
-        <v>0.2963861</v>
+        <v>0.2964294000000001</v>
       </c>
       <c r="D3">
-        <v>0.2543214</v>
+        <v>0.2543192</v>
       </c>
       <c r="E3">
-        <v>0.1359233</v>
+        <v>0.1361027</v>
       </c>
       <c r="F3">
-        <v>0.04673090000000002</v>
+        <v>0.04666709999999996</v>
       </c>
       <c r="G3">
-        <v>0.01002979999999998</v>
+        <v>0.01003450000000006</v>
       </c>
       <c r="H3">
-        <v>0.001208700000000063</v>
+        <v>0.001232299999999964</v>
       </c>
       <c r="I3">
-        <v>6.669999999997511E-05</v>
+        <v>6.499999999998174E-05</v>
       </c>
     </row>
   </sheetData>
